--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.01_Q4_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.01_Q4_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0009892818935632974</v>
+        <v>0.0002378140409351064</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009892818935632974</v>
+        <v>0.0002378140409351064</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0009884320258364322</v>
+        <v>0.000237566005953924</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009884320258364322</v>
+        <v>0.000237566005953924</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0009867472898953606</v>
+        <v>0.0002370789601584196</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0009867472898953606</v>
+        <v>0.0002370789601584196</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0009839672341355396</v>
+        <v>0.0002362989686741243</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009839672341355396</v>
+        <v>0.0002362989686741243</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0009805118910753341</v>
+        <v>0.0002353340975864574</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009805118910753341</v>
+        <v>0.0002353340975864574</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0009764088040127949</v>
+        <v>0.0002341973628302871</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0009764088040127949</v>
+        <v>0.0002341973628302871</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0009716126416676613</v>
+        <v>0.0002328583919230379</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009716126416676613</v>
+        <v>0.0002328583919230379</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0009665824387079944</v>
+        <v>0.0002314902203433472</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009665824387079944</v>
+        <v>0.0002314902203433472</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0009613412149910132</v>
+        <v>0.0002300792551050558</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0009613412149910132</v>
+        <v>0.0002300792551050558</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0009561488763576626</v>
+        <v>0.0002286963867805347</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0009561488763576626</v>
+        <v>0.0002286963867805347</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0009511675881283261</v>
+        <v>0.0002274068199787042</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0009511675881283261</v>
+        <v>0.0002274068199787042</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0009468218939875782</v>
+        <v>0.0002262766367048983</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0009468218939875782</v>
+        <v>0.0002262766367048983</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0009432320442344496</v>
+        <v>0.0002253616379589529</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0009432320442344496</v>
+        <v>0.0002253616379589529</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0009405717270046898</v>
+        <v>0.000224695785440834</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0009405717270046898</v>
+        <v>0.000224695785440834</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0009389643294279774</v>
+        <v>0.0002243206290776522</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0009389643294279774</v>
+        <v>0.0002243206290776522</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0009386837120538675</v>
+        <v>0.000224280452456132</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0009386837120538675</v>
+        <v>0.000224280452456132</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0009397874234795193</v>
+        <v>0.0002246276990979557</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0009397874234795193</v>
+        <v>0.0002246276990979557</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0009425855849895028</v>
+        <v>0.0002254183806672362</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0009425855849895028</v>
+        <v>0.0002254183806672362</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0009472075892324958</v>
+        <v>0.0002267063208107454</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0009472075892324958</v>
+        <v>0.0002267063208107454</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0009550123298368327</v>
+        <v>0.0002287685151047112</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0009550123298368327</v>
+        <v>0.0002287685151047112</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0009646445877124126</v>
+        <v>0.0002313124634989868</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0009646445877124126</v>
+        <v>0.0002313124634989868</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0009761267172803512</v>
+        <v>0.00023434583410581</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0009761267172803512</v>
+        <v>0.00023434583410581</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0009905324232377054</v>
+        <v>0.0002380821222424346</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0009905324232377054</v>
+        <v>0.0002380821222424346</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.001007312903383064</v>
+        <v>0.0002424147262165071</v>
       </c>
       <c r="C25" t="n">
-        <v>0.001007312903383064</v>
+        <v>0.0002424147262165071</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.001026964510275313</v>
+        <v>0.0002474970171174609</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001026964510275313</v>
+        <v>0.0002474970171174609</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.001049873310941149</v>
+        <v>0.0002533855800911413</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001049873310941149</v>
+        <v>0.0002533855800911413</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.001075832768284514</v>
+        <v>0.0002600470824385506</v>
       </c>
       <c r="C28" t="n">
-        <v>0.001075832768284514</v>
+        <v>0.0002600470824385506</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.00110509593635363</v>
+        <v>0.0002675150857003167</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00110509593635363</v>
+        <v>0.0002675150857003167</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.001137742392958479</v>
+        <v>0.0002758217610088437</v>
       </c>
       <c r="C30" t="n">
-        <v>0.001137742392958479</v>
+        <v>0.0002758217610088437</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.00117381682056045</v>
+        <v>0.0002849845817786774</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00117381682056045</v>
+        <v>0.0002849845817786774</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
